--- a/IN_final.xlsx
+++ b/IN_final.xlsx
@@ -1096,70 +1096,70 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2188738.88</v>
+        <v>7538439.07</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1658899.5</v>
+        <v>4311831.59</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>2018028.76</v>
+        <v>5682519.48</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>161617.4</v>
+        <v>3164952.59</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>316401.81</v>
+        <v>3249117.34</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>245482</v>
+        <v>2395955.06</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>156085.08</v>
+        <v>1953279.96</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>123843.07</v>
+        <v>2573127.52</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>178042.63</v>
+        <v>4406069.06</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>187477.13</v>
+        <v>4026243.05</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>181773.46</v>
+        <v>4938095.29</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>258589.86</v>
+        <v>4601192.080000001</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>197129.18</v>
+        <v>5069641.59</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>102617.68</v>
+        <v>3188147.18</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>202157.02</v>
+        <v>4941849.119999999</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>138428.14</v>
+        <v>2660507.39</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>226012.05</v>
+        <v>3066265.06</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>320327.63</v>
+        <v>2556131.48</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>104116.97</v>
+        <v>1454152.83</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>101193.41</v>
+        <v>1953717.05</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>194705.88</v>
+        <v>3315589.01</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>289979.17</v>
+        <v>3348683.84</v>
       </c>
     </row>
     <row r="10">
@@ -1982,70 +1982,70 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>207892.9</v>
+        <v>742912.5800000001</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>213131.12</v>
+        <v>382579</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>138952.61</v>
+        <v>228909.11</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31796.66</v>
+        <v>210033.89</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>51789.65</v>
+        <v>482405.14</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0</v>
+        <v>207290.67</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>12969.93</v>
+        <v>342329.7</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14937.55</v>
+        <v>507090.65</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39874.78</v>
+        <v>924240.3800000001</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>9281.98</v>
+        <v>242062.09</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>4302.07</v>
+        <v>584141.61</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>15953.94</v>
+        <v>121648.53</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>5940.31</v>
+        <v>235547.31</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>16895.61</v>
+        <v>321002.09</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>19765.37</v>
+        <v>241984.27</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>4828.14</v>
+        <v>165074.52</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>17984.85</v>
+        <v>292285.9399999999</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>0</v>
+        <v>351091.31</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0</v>
+        <v>210291.23</v>
       </c>
       <c r="U9" s="2" t="n">
-        <v>18622.15</v>
+        <v>464856.38</v>
       </c>
       <c r="V9" s="2" t="n">
-        <v>52573.07</v>
+        <v>477295.73</v>
       </c>
       <c r="W9" s="2" t="n">
-        <v>70758.82000000001</v>
+        <v>504861.31</v>
       </c>
     </row>
     <row r="10">
@@ -2868,70 +2868,70 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.09498296114701449</v>
+        <v>0.09854992168823089</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.1284774152985157</v>
+        <v>0.08872772324579588</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.06885561432732008</v>
+        <v>0.04028303128667849</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.1967403262272503</v>
+        <v>0.06636241271468776</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.1636831660349857</v>
+        <v>0.1484726741201658</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>0.08651692740847985</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.08309525804772629</v>
+        <v>0.1752589014428838</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.1206167611962462</v>
+        <v>0.197071713725249</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.2239619803414497</v>
+        <v>0.2097652958712364</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.04950993222479989</v>
+        <v>0.0601210823574101</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.02366720642276381</v>
+        <v>0.1182928995280688</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.06169592264754697</v>
+        <v>0.02643848113378479</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.03013409785400619</v>
+        <v>0.04646232003158236</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0.1646461896234645</v>
+        <v>0.1006860950503546</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0.09777236526339773</v>
+        <v>0.04896634116583471</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0.03487831303664125</v>
+        <v>0.06204625501904733</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0.07957473948844762</v>
+        <v>0.09532311599963245</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>0</v>
+        <v>0.1373526020656809</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>0</v>
+        <v>0.1446142562608086</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>0.1840253233881534</v>
+        <v>0.237934341618199</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>0.2700127494865589</v>
+        <v>0.1439550344027712</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>0.2440134579321681</v>
+        <v>0.1507641013969238</v>
       </c>
     </row>
     <row r="10">
